--- a/data/trans_camb/P2B_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,49; 36,28</t>
+          <t>25,32; 36,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,73; 32,03</t>
+          <t>21,13; 32,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 7,16</t>
+          <t>-3,31; 7,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,78; 34,71</t>
+          <t>24,02; 34,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,47; 27,59</t>
+          <t>17,77; 28,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 2,98</t>
+          <t>-8,72; 3,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,93; 33,93</t>
+          <t>26,22; 33,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,06; 28,37</t>
+          <t>20,47; 28,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 3,52</t>
+          <t>-4,65; 3,56</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>100,08; 190,46</t>
+          <t>102,26; 188,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,19; 167,43</t>
+          <t>84,75; 165,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 35,32</t>
+          <t>-13,73; 38,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81,45; 148,16</t>
+          <t>85,5; 150,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,23; 118,62</t>
+          <t>62,24; 122,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,85; 12,62</t>
+          <t>-31,93; 12,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,45; 151,34</t>
+          <t>100,57; 154,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,35; 126,67</t>
+          <t>79,71; 127,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 15,67</t>
+          <t>-17,67; 15,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,34; 36,8</t>
+          <t>27,9; 37,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,71; 25,5</t>
+          <t>16,41; 26,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 7,36</t>
+          <t>-1,33; 7,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,97; 35,09</t>
+          <t>26,05; 35,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,2; 28,19</t>
+          <t>18,97; 28,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 11,86</t>
+          <t>3,34; 11,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,04; 34,88</t>
+          <t>28,06; 34,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,25; 25,9</t>
+          <t>19,07; 25,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 8,56</t>
+          <t>2,37; 8,77</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>107,45; 181,96</t>
+          <t>108,84; 190,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,34; 126,03</t>
+          <t>65,77; 129,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 36,12</t>
+          <t>-5,62; 41,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92,55; 152,01</t>
+          <t>92,23; 154,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,72; 121,93</t>
+          <t>67,34; 123,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,76; 51,53</t>
+          <t>11,64; 49,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>106,68; 154,44</t>
+          <t>108,39; 155,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73,65; 114,84</t>
+          <t>73,09; 113,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 38,1</t>
+          <t>8,93; 39,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,84; 39,71</t>
+          <t>28,16; 39,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 18,87</t>
+          <t>7,42; 18,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 6,23</t>
+          <t>-4,88; 6,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,88; 38,42</t>
+          <t>27,61; 37,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,59; 20,54</t>
+          <t>10,63; 21,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 49,36</t>
+          <t>-4,7; 48,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,06; 37,01</t>
+          <t>29,52; 36,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,48; 18,2</t>
+          <t>10,87; 18,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 35,8</t>
+          <t>-2,59; 35,96</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>113,67; 215,19</t>
+          <t>115,41; 220,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,02; 99,25</t>
+          <t>31,09; 102,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 32,83</t>
+          <t>-21,41; 32,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94,72; 169,11</t>
+          <t>97,51; 167,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,93; 89,3</t>
+          <t>37,04; 96,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 201,79</t>
+          <t>-18,24; 201,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>113,22; 172,46</t>
+          <t>116,94; 174,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40,44; 83,91</t>
+          <t>42,71; 84,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 162,13</t>
+          <t>-10,44; 167,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,2; 28,04</t>
+          <t>18,74; 28,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,35; 23,66</t>
+          <t>14,14; 23,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 3,39</t>
+          <t>-5,48; 3,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,27; 25,56</t>
+          <t>16,64; 25,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,82; 25,24</t>
+          <t>15,72; 25,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,69; -0,7</t>
+          <t>-11,59; -0,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,7; 25,34</t>
+          <t>18,85; 25,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,85; 23,34</t>
+          <t>16,33; 23,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,76; -0,19</t>
+          <t>-7,18; -0,06</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>76,03; 149,3</t>
+          <t>78,71; 148,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>59,91; 125,14</t>
+          <t>60,11; 120,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 18,23</t>
+          <t>-23,35; 16,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54,7; 101,79</t>
+          <t>55,67; 102,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,25; 100,06</t>
+          <t>52,9; 100,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,67; -2,92</t>
+          <t>-40,35; -3,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,2; 110,53</t>
+          <t>71,82; 110,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>63,92; 101,56</t>
+          <t>62,05; 101,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,58; -0,95</t>
+          <t>-27,94; -0,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27,45; 32,49</t>
+          <t>27,2; 32,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,05; 22,27</t>
+          <t>17,23; 22,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,51</t>
+          <t>-1,1; 3,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,42; 30,36</t>
+          <t>25,58; 30,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,14; 23,18</t>
+          <t>18,41; 23,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 20,34</t>
+          <t>-1,32; 22,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,12; 30,64</t>
+          <t>27,11; 30,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,53; 22,07</t>
+          <t>18,61; 22,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 13,71</t>
+          <t>-0,44; 13,45</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>119,86; 159,06</t>
+          <t>116,73; 157,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>73,94; 108,89</t>
+          <t>74,92; 109,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 17,22</t>
+          <t>-5,03; 17,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92,78; 122,01</t>
+          <t>93,03; 121,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>66,52; 92,55</t>
+          <t>67,15; 93,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 76,87</t>
+          <t>-5,01; 87,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>107,43; 131,19</t>
+          <t>108,24; 132,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>73,85; 94,31</t>
+          <t>74,07; 94,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 55,7</t>
+          <t>-1,95; 58,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>0,97</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,32; 36,2</t>
+          <t>25,25; 36,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,13; 32,11</t>
+          <t>21,27; 32,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 7,33</t>
+          <t>-3,76; 6,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,02; 34,79</t>
+          <t>24,21; 35,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 28,72</t>
+          <t>17,15; 28,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 3,15</t>
+          <t>-4,92; 4,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,22; 33,91</t>
+          <t>25,88; 33,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,47; 28,24</t>
+          <t>20,55; 28,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,56</t>
+          <t>-3,02; 4,55</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-7,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-0,76%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>102,26; 188,86</t>
+          <t>99,71; 187,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,75; 165,06</t>
+          <t>85,75; 165,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 38,98</t>
+          <t>-15,23; 34,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85,5; 150,55</t>
+          <t>83,3; 152,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,24; 122,29</t>
+          <t>60,33; 123,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 12,55</t>
+          <t>-16,85; 19,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100,57; 154,93</t>
+          <t>97,68; 153,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>79,71; 127,83</t>
+          <t>77,7; 125,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 15,32</t>
+          <t>-11,57; 20,42</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,68</t>
+          <t>7,53</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>6,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,9; 37,52</t>
+          <t>27,58; 36,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 26,43</t>
+          <t>16,34; 25,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 7,99</t>
+          <t>0,56; 10,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,05; 35,25</t>
+          <t>26,29; 35,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,97; 28,75</t>
+          <t>19,65; 28,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 11,82</t>
+          <t>3,25; 11,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,06; 34,76</t>
+          <t>28,01; 34,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,07; 25,58</t>
+          <t>19,1; 25,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,77</t>
+          <t>3,36; 9,87</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>108,84; 190,01</t>
+          <t>110,45; 183,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,77; 129,92</t>
+          <t>64,57; 124,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 41,07</t>
+          <t>2,16; 47,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92,23; 154,12</t>
+          <t>92,84; 149,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,34; 123,74</t>
+          <t>69,88; 121,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 49,55</t>
+          <t>11,25; 47,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>108,39; 155,22</t>
+          <t>107,61; 152,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73,09; 113,96</t>
+          <t>73,51; 114,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,93; 39,0</t>
+          <t>12,8; 43,07</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,05</t>
+          <t>-1,31</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,17</t>
+          <t>-0,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,16; 39,78</t>
+          <t>28,16; 39,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 18,77</t>
+          <t>7,34; 18,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 6,09</t>
+          <t>-4,67; 6,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,61; 37,73</t>
+          <t>27,5; 37,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,63; 21,64</t>
+          <t>10,22; 20,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 48,91</t>
+          <t>-5,79; 3,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,52; 36,99</t>
+          <t>29,34; 36,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,87; 18,15</t>
+          <t>10,42; 18,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 35,96</t>
+          <t>-3,74; 3,65</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>-5,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>-0,63%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>115,41; 220,44</t>
+          <t>115,9; 212,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,09; 102,5</t>
+          <t>30,41; 99,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 32,27</t>
+          <t>-19,47; 34,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97,51; 167,07</t>
+          <t>97,79; 163,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37,04; 96,16</t>
+          <t>37,55; 91,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 201,0</t>
+          <t>-20,99; 15,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>116,94; 174,18</t>
+          <t>114,71; 172,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,71; 84,27</t>
+          <t>40,76; 83,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 167,82</t>
+          <t>-14,8; 17,09</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,02</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,28</t>
+          <t>-0,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,74; 28,57</t>
+          <t>19,15; 28,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,14; 23,34</t>
+          <t>14,04; 23,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 3,29</t>
+          <t>-4,36; 4,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,64; 25,68</t>
+          <t>16,48; 25,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,72; 25,11</t>
+          <t>15,69; 24,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -0,59</t>
+          <t>-5,38; 2,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,85; 25,52</t>
+          <t>19,03; 25,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,33; 23,28</t>
+          <t>16,44; 23,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -0,06</t>
+          <t>-3,72; 2,2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-5,26%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-18,4%</t>
+          <t>-4,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-13,29%</t>
+          <t>-2,63%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>78,71; 148,55</t>
+          <t>80,21; 151,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>60,11; 120,62</t>
+          <t>60,98; 126,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 16,97</t>
+          <t>-18,23; 24,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55,67; 102,64</t>
+          <t>54,08; 101,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>52,9; 100,06</t>
+          <t>53,8; 98,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,35; -3,07</t>
+          <t>-18,61; 11,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,82; 110,56</t>
+          <t>72,22; 110,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>62,05; 101,59</t>
+          <t>62,16; 100,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,94; -0,15</t>
+          <t>-14,04; 9,86</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>2,21</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>1,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27,2; 32,3</t>
+          <t>27,12; 32,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,23; 22,45</t>
+          <t>17,05; 22,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,61</t>
+          <t>-0,45; 4,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,58; 30,47</t>
+          <t>25,8; 30,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,41; 23,39</t>
+          <t>18,2; 23,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 22,42</t>
+          <t>-0,67; 3,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,11; 30,69</t>
+          <t>26,97; 30,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,61; 22,06</t>
+          <t>18,25; 21,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 13,45</t>
+          <t>0,25; 3,48</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>116,73; 157,04</t>
+          <t>117,32; 159,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>74,92; 109,56</t>
+          <t>73,49; 108,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 17,72</t>
+          <t>-1,61; 22,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93,03; 121,8</t>
+          <t>93,74; 123,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>67,15; 93,4</t>
+          <t>66,44; 92,38</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 87,69</t>
+          <t>-2,43; 14,72</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>108,24; 132,25</t>
+          <t>107,28; 131,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>74,07; 94,77</t>
+          <t>73,18; 94,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 58,2</t>
+          <t>0,97; 14,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
